--- a/docs/PRAP_UI_Component_List_v0.5.xlsx
+++ b/docs/PRAP_UI_Component_List_v0.5.xlsx
@@ -590,7 +590,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Dan — v0.3 reviewed 2026-08-01</t>
+          <t>Dan — v0.3 reviewed 2026-08-01, v0.4 reviewed 2026-08-02</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>44 components. 29 Keep, 9 Change (amber), 6 added by those changes (green). Your comments are quoted exactly as written.</t>
+          <t>45 components. 28 Keep, 12 Change (amber), 5 added by those changes (green). Your comments are quoted exactly as written.</t>
         </is>
       </c>
     </row>
